--- a/plantillas/consulta/Reporte_UT-VPV.xlsx
+++ b/plantillas/consulta/Reporte_UT-VPV.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Visual Studio Code\NodeJS\SIVACC\plantillas\consulta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45301C4B-4F2B-43D8-9A70-F7495FDD33FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5349EF4-E8BB-42C5-919A-BD951E52A1DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -98,7 +98,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -108,12 +108,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="22"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC0C0C0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -177,9 +171,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -188,6 +179,9 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -511,16 +505,16 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:8" ht="20.25" x14ac:dyDescent="0.2">
-      <c r="B2" s="13"/>
+      <c r="B2" s="12"/>
       <c r="C2" s="11"/>
     </row>
-    <row r="3" spans="1:8" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="15"/>
+    <row r="3" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B3" s="14"/>
       <c r="C3" s="11"/>
     </row>
     <row r="5" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="7"/>
-      <c r="B5" s="14"/>
+      <c r="B5" s="13"/>
       <c r="C5" s="7"/>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
@@ -530,7 +524,7 @@
     </row>
     <row r="6" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8"/>
-      <c r="B6" s="14"/>
+      <c r="B6" s="13"/>
       <c r="C6" s="8"/>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
@@ -544,7 +538,7 @@
       <c r="F7" s="3"/>
     </row>
     <row r="8" spans="1:8" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="15" t="s">
         <v>4</v>
       </c>
       <c r="C8" s="9" t="s">
